--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 04_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 04_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AA5014-C7B2-45B7-8BD8-3A19F680DB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1324DA98-244D-4462-8D61-70CF75847D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -384,6 +384,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -413,30 +437,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -879,16 +879,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -1549,10 +1549,10 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="23"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="3">
         <f>SUM(C3:C22)</f>
         <v>79</v>
@@ -1618,88 +1618,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
-      <c r="AH1" s="24"/>
+      <c r="A1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="33"/>
+      <c r="AD2" s="33"/>
+      <c r="AE2" s="33"/>
+      <c r="AF2" s="33"/>
+      <c r="AG2" s="33"/>
+      <c r="AH2" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="5">
         <v>1</v>
       </c>
@@ -1793,7 +1793,7 @@
       <c r="AG3" s="5">
         <v>31</v>
       </c>
-      <c r="AH3" s="25"/>
+      <c r="AH3" s="33"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
@@ -2709,52 +2709,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="28"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="36"/>
       <c r="C2" s="5">
         <v>1</v>
       </c>
@@ -2848,7 +2848,7 @@
       <c r="AG2" s="5">
         <v>31</v>
       </c>
-      <c r="AH2" s="25"/>
+      <c r="AH2" s="33"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -3789,490 +3789,490 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="31"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="31"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="31"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="21"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="32"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="31"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="21"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="31"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="31"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="31"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="31"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="31"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="31"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="31"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="31"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="31"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="31"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="31"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="31"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="31"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="32"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
+      <c r="A37" s="25"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="36"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="32"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="34"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="32"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="34"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="32"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="32"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="32"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="32"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="37"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="27"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="35"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="37"/>
+      <c r="A52" s="25"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="27"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="37"/>
+      <c r="A53" s="26"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="27"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="32"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="37"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="27"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="32"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="37"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="27"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
@@ -4444,52 +4444,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="5">
         <v>1</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="AG2" s="5">
         <v>31</v>
       </c>
-      <c r="AH2" s="25"/>
+      <c r="AH2" s="33"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -5448,16 +5448,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -5975,10 +5975,10 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="29"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="10">
         <f>SUM(C3:C17)</f>
         <v>79</v>
